--- a/www/ig/fhir/sdo/all-profiles.xlsx
+++ b/www/ig/fhir/sdo/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.0.6</t>
+    <t>4.0.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T14:22:03+00:00</t>
+    <t>2026-06-29T08:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -346,7 +346,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -959,7 +959,7 @@
     <t>Consent.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -997,7 +997,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -1021,7 +1021,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -1160,7 +1160,7 @@
     <t>The four anticipated uses for the Consent Resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-scope</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-scope|4.0.1</t>
   </si>
   <si>
     <t>Consent.category</t>
@@ -1183,13 +1183,13 @@
     <t>A classification of the type of consents found in a consent statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-category|4.0.1</t>
   </si>
   <si>
     <t>Consent.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -1225,7 +1225,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1245,7 +1245,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1259,7 +1259,7 @@
   </si>
   <si>
     <t>Attachment
-Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)</t>
+Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
   </si>
   <si>
     <t>Source from which this consent is taken</t>
@@ -1329,7 +1329,7 @@
     <t>Regulatory policy examples.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy|4.0.1</t>
   </si>
   <si>
     <t>Consent.verification</t>
@@ -1366,7 +1366,7 @@
     <t>Consent.verification.verifiedWith</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1464,13 +1464,13 @@
     <t>How an actor is involved in the consent considerations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
+    <t>http://hl7.org/fhir/ValueSet/security-role-type|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.actor.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Group|CareTeam|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Device|4.0.1|Group|4.0.1|CareTeam|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1498,7 +1498,7 @@
     <t>Detailed codes for the consent action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-action</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-action|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
@@ -1546,7 +1546,7 @@
     <t>The class (type) of information a consent rule covers.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-class</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-class|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.code</t>
@@ -1564,7 +1564,7 @@
     <t>If this code is found in an instance, then the exception applies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-code</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-code|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -1672,7 +1672,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1747,7 +1747,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -2135,13 +2135,13 @@
     <t>High-level kind of a clinical document at a macro level.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
+    <t>http://hl7.org/fhir/ValueSet/document-classcodes|4.0.1</t>
   </si>
   <si>
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|Group|Device)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|Group|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -2170,7 +2170,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Device|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -2186,7 +2186,7 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -2251,6 +2251,10 @@
   </si>
   <si>
     <t>DocumentReference.relatesTo.target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1)
+</t>
   </si>
   <si>
     <t>Target of the relationship</t>
@@ -2500,7 +2504,7 @@
     <t>Document Format Codes.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/formatcodes</t>
+    <t>http://hl7.org/fhir/ValueSet/formatcodes|4.0.1</t>
   </si>
   <si>
     <t>DocumentReference.context</t>
@@ -2527,7 +2531,7 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -2576,7 +2580,7 @@
     <t>XDS Facility Type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes|4.0.1</t>
   </si>
   <si>
     <t>DocumentReference.context.practiceSetting</t>
@@ -2597,7 +2601,7 @@
     <t>Additional details about where the content was created (e.g. clinical specialty).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
   </si>
   <si>
     <t>DocumentReference.context.sourcePatientInfo</t>
@@ -2612,7 +2616,7 @@
     <t>DocumentReference.context.related</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -2710,7 +2714,7 @@
     <t>Task.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -2756,7 +2760,7 @@
     <t>Task.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Task)
+    <t xml:space="preserve">Reference(Task|4.0.1)
 </t>
   </si>
   <si>
@@ -2878,7 +2882,7 @@
     <t>Codes to identify what the task involves.  These will typically be specific to a particular workflow.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-code</t>
+    <t>http://hl7.org/fhir/ValueSet/task-code|4.0.1</t>
   </si>
   <si>
     <t>Task.description</t>
@@ -2924,7 +2928,7 @@
     <t>Task.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -2985,7 +2989,7 @@
     <t>Task.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson)
+    <t xml:space="preserve">Reference(Device|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -3013,7 +3017,7 @@
     <t>The type(s) of task performers allowed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
+    <t>http://hl7.org/fhir/ValueSet/performer-role|4.0.1</t>
   </si>
   <si>
     <t>Task.owner</t>
@@ -3023,7 +3027,7 @@
 Executer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -3042,7 +3046,7 @@
     <t>Task.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -3082,7 +3086,7 @@
     <t>Task.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
 </t>
   </si>
   <si>
@@ -3112,7 +3116,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -3180,7 +3184,7 @@
     <t>Task.restriction.recipient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Group|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Group|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -3603,10 +3607,6 @@
   </si>
   <si>
     <t>Permet de définir le mode de prise en charge</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-regle-ModePriseEnCharge:Les codes possibles pour le mode de prise en charge sont : 46 (Hébergement (accueil jour et nuit)) ; 47 (Accueil de jour); 48 (Accueil de nuit) {(value.coding.where(code='48').exists()) or (value.coding.where(code='47').exists()) or (value.coding.where(code='46').exists())}</t>
   </si>
   <si>
     <t>Task.input:modePriseCharge.id</t>
@@ -4661,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="87">
@@ -4669,7 +4669,7 @@
         <v>4</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="88">
@@ -4685,7 +4685,7 @@
         <v>8</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="90">
@@ -4745,7 +4745,7 @@
         <v>22</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="98">
@@ -4781,7 +4781,7 @@
         <v>30</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="103">
@@ -4789,7 +4789,7 @@
         <v>32</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="104">
@@ -4818,17 +4818,17 @@
   <dimension ref="A1:AK417"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.96484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="52.484375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="50.828125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="21.4453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="39.9140625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="16.27734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="41.98046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.99609375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="43.578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.38671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="34.21875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.4453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="12.3828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4837,21 +4837,21 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="96.98046875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="55.12890625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="169.1328125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="123.671875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="17.21484375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="44.0703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="10.5546875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="83.14453125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="47.265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="145.00390625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="106.02734375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="14.7578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.046875" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -28217,13 +28217,13 @@
         <v>83</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>510</v>
+        <v>716</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" s="2"/>
@@ -28294,10 +28294,10 @@
         <v>582</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" t="s" s="2">
@@ -28323,16 +28323,16 @@
         <v>140</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="O225" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="P225" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="Q225" t="s" s="2">
         <v>74</v>
@@ -28381,7 +28381,7 @@
         <v>74</v>
       </c>
       <c r="AG225" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AH225" t="s" s="2">
         <v>75</v>
@@ -28401,10 +28401,10 @@
         <v>582</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -28430,16 +28430,16 @@
         <v>357</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O226" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="P226" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="Q226" t="s" s="2">
         <v>74</v>
@@ -28488,7 +28488,7 @@
         <v>74</v>
       </c>
       <c r="AG226" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AH226" t="s" s="2">
         <v>75</v>
@@ -28508,10 +28508,10 @@
         <v>582</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" t="s" s="2">
@@ -28537,10 +28537,10 @@
         <v>135</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O227" s="2"/>
       <c r="P227" s="2"/>
@@ -28591,7 +28591,7 @@
         <v>74</v>
       </c>
       <c r="AG227" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AH227" t="s" s="2">
         <v>82</v>
@@ -28611,10 +28611,10 @@
         <v>582</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" t="s" s="2">
@@ -28714,10 +28714,10 @@
         <v>582</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" t="s" s="2">
@@ -28819,10 +28819,10 @@
         <v>582</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" t="s" s="2">
@@ -28926,10 +28926,10 @@
         <v>582</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" t="s" s="2">
@@ -28952,13 +28952,13 @@
         <v>83</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O231" s="2"/>
       <c r="P231" s="2"/>
@@ -29009,7 +29009,7 @@
         <v>74</v>
       </c>
       <c r="AG231" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AH231" t="s" s="2">
         <v>82</v>
@@ -29029,10 +29029,10 @@
         <v>582</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -29132,10 +29132,10 @@
         <v>582</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -29237,10 +29237,10 @@
         <v>582</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
@@ -29266,14 +29266,14 @@
         <v>102</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="O234" s="2"/>
       <c r="P234" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="Q234" t="s" s="2">
         <v>74</v>
@@ -29286,7 +29286,7 @@
         <v>74</v>
       </c>
       <c r="U234" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="V234" t="s" s="2">
         <v>74</v>
@@ -29301,10 +29301,10 @@
         <v>120</v>
       </c>
       <c r="Z234" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AA234" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AB234" t="s" s="2">
         <v>74</v>
@@ -29322,7 +29322,7 @@
         <v>74</v>
       </c>
       <c r="AG234" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AH234" t="s" s="2">
         <v>75</v>
@@ -29342,10 +29342,10 @@
         <v>582</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -29371,14 +29371,14 @@
         <v>102</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="Q235" t="s" s="2">
         <v>74</v>
@@ -29391,7 +29391,7 @@
         <v>74</v>
       </c>
       <c r="U235" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="V235" t="s" s="2">
         <v>74</v>
@@ -29427,7 +29427,7 @@
         <v>74</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AH235" t="s" s="2">
         <v>75</v>
@@ -29447,10 +29447,10 @@
         <v>582</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -29473,19 +29473,19 @@
         <v>74</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="O236" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="P236" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="Q236" t="s" s="2">
         <v>74</v>
@@ -29534,7 +29534,7 @@
         <v>74</v>
       </c>
       <c r="AG236" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AH236" t="s" s="2">
         <v>75</v>
@@ -29554,10 +29554,10 @@
         <v>582</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" t="s" s="2">
@@ -29580,19 +29580,19 @@
         <v>83</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O237" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P237" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="Q237" t="s" s="2">
         <v>74</v>
@@ -29605,7 +29605,7 @@
         <v>74</v>
       </c>
       <c r="U237" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="V237" t="s" s="2">
         <v>74</v>
@@ -29641,7 +29641,7 @@
         <v>74</v>
       </c>
       <c r="AG237" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AH237" t="s" s="2">
         <v>75</v>
@@ -29661,10 +29661,10 @@
         <v>582</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" t="s" s="2">
@@ -29690,16 +29690,16 @@
         <v>129</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N238" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="O238" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="P238" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Q238" t="s" s="2">
         <v>74</v>
@@ -29748,7 +29748,7 @@
         <v>74</v>
       </c>
       <c r="AG238" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AH238" t="s" s="2">
         <v>75</v>
@@ -29768,10 +29768,10 @@
         <v>582</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" t="s" s="2">
@@ -29794,19 +29794,19 @@
         <v>83</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O239" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="P239" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Q239" t="s" s="2">
         <v>74</v>
@@ -29855,7 +29855,7 @@
         <v>74</v>
       </c>
       <c r="AG239" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AH239" t="s" s="2">
         <v>75</v>
@@ -29875,10 +29875,10 @@
         <v>582</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" t="s" s="2">
@@ -29904,14 +29904,14 @@
         <v>140</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N240" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="Q240" t="s" s="2">
         <v>74</v>
@@ -29924,7 +29924,7 @@
         <v>74</v>
       </c>
       <c r="U240" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="V240" t="s" s="2">
         <v>74</v>
@@ -29960,7 +29960,7 @@
         <v>74</v>
       </c>
       <c r="AG240" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AH240" t="s" s="2">
         <v>75</v>
@@ -29980,10 +29980,10 @@
         <v>582</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" t="s" s="2">
@@ -30009,14 +30009,14 @@
         <v>375</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N241" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="Q241" t="s" s="2">
         <v>74</v>
@@ -30065,7 +30065,7 @@
         <v>74</v>
       </c>
       <c r="AG241" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AH241" t="s" s="2">
         <v>75</v>
@@ -30085,10 +30085,10 @@
         <v>582</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" t="s" s="2">
@@ -30114,13 +30114,13 @@
         <v>306</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N242" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O242" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="P242" s="2"/>
       <c r="Q242" t="s" s="2">
@@ -30149,10 +30149,10 @@
         <v>106</v>
       </c>
       <c r="Z242" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AA242" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AB242" t="s" s="2">
         <v>74</v>
@@ -30170,7 +30170,7 @@
         <v>74</v>
       </c>
       <c r="AG242" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AH242" t="s" s="2">
         <v>75</v>
@@ -30190,10 +30190,10 @@
         <v>582</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" t="s" s="2">
@@ -30219,13 +30219,13 @@
         <v>135</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="O243" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="P243" s="2"/>
       <c r="Q243" t="s" s="2">
@@ -30275,7 +30275,7 @@
         <v>74</v>
       </c>
       <c r="AG243" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AH243" t="s" s="2">
         <v>75</v>
@@ -30295,10 +30295,10 @@
         <v>582</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D244" s="2"/>
       <c r="E244" t="s" s="2">
@@ -30398,10 +30398,10 @@
         <v>582</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D245" s="2"/>
       <c r="E245" t="s" s="2">
@@ -30503,10 +30503,10 @@
         <v>582</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D246" s="2"/>
       <c r="E246" t="s" s="2">
@@ -30610,10 +30610,10 @@
         <v>582</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D247" s="2"/>
       <c r="E247" t="s" s="2">
@@ -30636,13 +30636,13 @@
         <v>74</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="O247" s="2"/>
       <c r="P247" s="2"/>
@@ -30693,7 +30693,7 @@
         <v>74</v>
       </c>
       <c r="AG247" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AH247" t="s" s="2">
         <v>75</v>
@@ -30713,10 +30713,10 @@
         <v>582</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D248" s="2"/>
       <c r="E248" t="s" s="2">
@@ -30742,13 +30742,13 @@
         <v>357</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="N248" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="O248" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="P248" s="2"/>
       <c r="Q248" t="s" s="2">
@@ -30777,10 +30777,10 @@
         <v>318</v>
       </c>
       <c r="Z248" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AA248" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AB248" t="s" s="2">
         <v>74</v>
@@ -30798,7 +30798,7 @@
         <v>74</v>
       </c>
       <c r="AG248" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AH248" t="s" s="2">
         <v>75</v>
@@ -30818,10 +30818,10 @@
         <v>582</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D249" s="2"/>
       <c r="E249" t="s" s="2">
@@ -30847,10 +30847,10 @@
         <v>444</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="N249" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="O249" s="2"/>
       <c r="P249" s="2"/>
@@ -30901,7 +30901,7 @@
         <v>74</v>
       </c>
       <c r="AG249" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AH249" t="s" s="2">
         <v>75</v>
@@ -30921,10 +30921,10 @@
         <v>582</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D250" s="2"/>
       <c r="E250" t="s" s="2">
@@ -30950,10 +30950,10 @@
         <v>357</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N250" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="O250" s="2"/>
       <c r="P250" s="2"/>
@@ -30983,10 +30983,10 @@
         <v>318</v>
       </c>
       <c r="Z250" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AA250" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AB250" t="s" s="2">
         <v>74</v>
@@ -31004,7 +31004,7 @@
         <v>74</v>
       </c>
       <c r="AG250" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AH250" t="s" s="2">
         <v>75</v>
@@ -31024,10 +31024,10 @@
         <v>582</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D251" s="2"/>
       <c r="E251" t="s" s="2">
@@ -31053,16 +31053,16 @@
         <v>357</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N251" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="O251" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="P251" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="Q251" t="s" s="2">
         <v>74</v>
@@ -31090,10 +31090,10 @@
         <v>318</v>
       </c>
       <c r="Z251" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AA251" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AB251" t="s" s="2">
         <v>74</v>
@@ -31111,7 +31111,7 @@
         <v>74</v>
       </c>
       <c r="AG251" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AH251" t="s" s="2">
         <v>75</v>
@@ -31131,10 +31131,10 @@
         <v>582</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D252" s="2"/>
       <c r="E252" t="s" s="2">
@@ -31160,10 +31160,10 @@
         <v>370</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="N252" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="O252" s="2"/>
       <c r="P252" s="2"/>
@@ -31214,7 +31214,7 @@
         <v>74</v>
       </c>
       <c r="AG252" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AH252" t="s" s="2">
         <v>75</v>
@@ -31234,10 +31234,10 @@
         <v>582</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D253" s="2"/>
       <c r="E253" t="s" s="2">
@@ -31260,16 +31260,16 @@
         <v>74</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="N253" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="O253" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="P253" s="2"/>
       <c r="Q253" t="s" s="2">
@@ -31319,7 +31319,7 @@
         <v>74</v>
       </c>
       <c r="AG253" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AH253" t="s" s="2">
         <v>75</v>
@@ -31336,13 +31336,13 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D254" s="2"/>
       <c r="E254" t="s" s="2">
@@ -31422,7 +31422,7 @@
         <v>74</v>
       </c>
       <c r="AG254" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AH254" t="s" s="2">
         <v>75</v>
@@ -31434,18 +31434,18 @@
         <v>74</v>
       </c>
       <c r="AK254" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D255" s="2"/>
       <c r="E255" t="s" s="2">
@@ -31544,13 +31544,13 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D256" s="2"/>
       <c r="E256" t="s" s="2">
@@ -31647,13 +31647,13 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D257" s="2"/>
       <c r="E257" t="s" s="2">
@@ -31750,13 +31750,13 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D258" s="2"/>
       <c r="E258" t="s" s="2">
@@ -31855,13 +31855,13 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D259" s="2"/>
       <c r="E259" t="s" s="2">
@@ -31960,13 +31960,13 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D260" s="2"/>
       <c r="E260" t="s" s="2">
@@ -32065,13 +32065,13 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D261" s="2"/>
       <c r="E261" t="s" s="2">
@@ -32097,7 +32097,7 @@
         <v>96</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="N261" t="s" s="2">
         <v>296</v>
@@ -32170,13 +32170,13 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D262" s="2"/>
       <c r="E262" t="s" s="2">
@@ -32275,13 +32275,13 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D263" s="2"/>
       <c r="E263" t="s" s="2">
@@ -32380,13 +32380,13 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D264" s="2"/>
       <c r="E264" t="s" s="2">
@@ -32485,13 +32485,13 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D265" s="2"/>
       <c r="E265" t="s" s="2">
@@ -32590,13 +32590,13 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D266" s="2"/>
       <c r="E266" t="s" s="2">
@@ -32695,13 +32695,13 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D267" s="2"/>
       <c r="E267" t="s" s="2">
@@ -32800,13 +32800,13 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D268" s="2"/>
       <c r="E268" t="s" s="2">
@@ -32905,13 +32905,13 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D269" s="2"/>
       <c r="E269" t="s" s="2">
@@ -33010,13 +33010,13 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D270" s="2"/>
       <c r="E270" t="s" s="2">
@@ -33117,13 +33117,13 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D271" s="2"/>
       <c r="E271" t="s" s="2">
@@ -33149,10 +33149,10 @@
         <v>111</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="N271" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="O271" s="2"/>
       <c r="P271" s="2"/>
@@ -33203,7 +33203,7 @@
         <v>74</v>
       </c>
       <c r="AG271" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AH271" t="s" s="2">
         <v>75</v>
@@ -33220,13 +33220,13 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D272" s="2"/>
       <c r="E272" t="s" s="2">
@@ -33249,17 +33249,17 @@
         <v>83</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="N272" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="O272" s="2"/>
       <c r="P272" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="Q272" t="s" s="2">
         <v>74</v>
@@ -33308,7 +33308,7 @@
         <v>74</v>
       </c>
       <c r="AG272" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AH272" t="s" s="2">
         <v>75</v>
@@ -33325,13 +33325,13 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D273" s="2"/>
       <c r="E273" t="s" s="2">
@@ -33357,14 +33357,14 @@
         <v>96</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="N273" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="O273" s="2"/>
       <c r="P273" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="Q273" t="s" s="2">
         <v>74</v>
@@ -33413,7 +33413,7 @@
         <v>74</v>
       </c>
       <c r="AG273" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="AH273" t="s" s="2">
         <v>75</v>
@@ -33430,13 +33430,13 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D274" s="2"/>
       <c r="E274" t="s" s="2">
@@ -33459,13 +33459,13 @@
         <v>83</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="N274" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="O274" s="2"/>
       <c r="P274" s="2"/>
@@ -33516,7 +33516,7 @@
         <v>74</v>
       </c>
       <c r="AG274" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AH274" t="s" s="2">
         <v>75</v>
@@ -33533,13 +33533,13 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" t="s" s="2">
@@ -33565,14 +33565,14 @@
         <v>111</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="N275" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="O275" s="2"/>
       <c r="P275" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="Q275" t="s" s="2">
         <v>74</v>
@@ -33621,7 +33621,7 @@
         <v>74</v>
       </c>
       <c r="AG275" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AH275" t="s" s="2">
         <v>75</v>
@@ -33638,13 +33638,13 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" t="s" s="2">
@@ -33667,19 +33667,19 @@
         <v>83</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="O276" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="P276" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="Q276" t="s" s="2">
         <v>74</v>
@@ -33728,7 +33728,7 @@
         <v>74</v>
       </c>
       <c r="AG276" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="AH276" t="s" s="2">
         <v>75</v>
@@ -33745,13 +33745,13 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D277" s="2"/>
       <c r="E277" t="s" s="2">
@@ -33777,14 +33777,14 @@
         <v>102</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N277" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="O277" s="2"/>
       <c r="P277" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="Q277" t="s" s="2">
         <v>74</v>
@@ -33794,7 +33794,7 @@
         <v>74</v>
       </c>
       <c r="T277" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="U277" t="s" s="2">
         <v>74</v>
@@ -33812,10 +33812,10 @@
         <v>120</v>
       </c>
       <c r="Z277" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="AA277" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AB277" t="s" s="2">
         <v>74</v>
@@ -33833,7 +33833,7 @@
         <v>74</v>
       </c>
       <c r="AG277" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AH277" t="s" s="2">
         <v>82</v>
@@ -33850,13 +33850,13 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D278" s="2"/>
       <c r="E278" t="s" s="2">
@@ -33882,13 +33882,13 @@
         <v>357</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="N278" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="O278" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="P278" s="2"/>
       <c r="Q278" t="s" s="2">
@@ -33917,7 +33917,7 @@
         <v>318</v>
       </c>
       <c r="Z278" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="AA278" t="s" s="2">
         <v>74</v>
@@ -33938,7 +33938,7 @@
         <v>74</v>
       </c>
       <c r="AG278" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="AH278" t="s" s="2">
         <v>75</v>
@@ -33955,13 +33955,13 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D279" s="2"/>
       <c r="E279" t="s" s="2">
@@ -33987,14 +33987,14 @@
         <v>357</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="N279" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="O279" s="2"/>
       <c r="P279" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="Q279" t="s" s="2">
         <v>74</v>
@@ -34022,7 +34022,7 @@
         <v>318</v>
       </c>
       <c r="Z279" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="AA279" t="s" s="2">
         <v>74</v>
@@ -34043,7 +34043,7 @@
         <v>74</v>
       </c>
       <c r="AG279" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="AH279" t="s" s="2">
         <v>75</v>
@@ -34060,13 +34060,13 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D280" s="2"/>
       <c r="E280" t="s" s="2">
@@ -34092,13 +34092,13 @@
         <v>102</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="N280" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="O280" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="P280" s="2"/>
       <c r="Q280" t="s" s="2">
@@ -34109,7 +34109,7 @@
         <v>74</v>
       </c>
       <c r="T280" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="U280" t="s" s="2">
         <v>74</v>
@@ -34127,10 +34127,10 @@
         <v>120</v>
       </c>
       <c r="Z280" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="AA280" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AB280" t="s" s="2">
         <v>74</v>
@@ -34148,7 +34148,7 @@
         <v>74</v>
       </c>
       <c r="AG280" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="AH280" t="s" s="2">
         <v>82</v>
@@ -34165,13 +34165,13 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D281" s="2"/>
       <c r="E281" t="s" s="2">
@@ -34197,20 +34197,20 @@
         <v>102</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="N281" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="O281" s="2"/>
       <c r="P281" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="Q281" t="s" s="2">
         <v>74</v>
       </c>
       <c r="R281" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="S281" t="s" s="2">
         <v>74</v>
@@ -34234,10 +34234,10 @@
         <v>120</v>
       </c>
       <c r="Z281" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AA281" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="AB281" t="s" s="2">
         <v>74</v>
@@ -34255,7 +34255,7 @@
         <v>74</v>
       </c>
       <c r="AG281" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="AH281" t="s" s="2">
         <v>75</v>
@@ -34272,13 +34272,13 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D282" s="2"/>
       <c r="E282" t="s" s="2">
@@ -34304,13 +34304,13 @@
         <v>357</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="N282" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="O282" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="P282" s="2"/>
       <c r="Q282" t="s" s="2">
@@ -34339,10 +34339,10 @@
         <v>318</v>
       </c>
       <c r="Z282" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="AA282" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="AB282" t="s" s="2">
         <v>74</v>
@@ -34360,7 +34360,7 @@
         <v>74</v>
       </c>
       <c r="AG282" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="AH282" t="s" s="2">
         <v>75</v>
@@ -34377,13 +34377,13 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D283" s="2"/>
       <c r="E283" t="s" s="2">
@@ -34409,10 +34409,10 @@
         <v>140</v>
       </c>
       <c r="M283" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="N283" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="O283" s="2"/>
       <c r="P283" s="2"/>
@@ -34463,7 +34463,7 @@
         <v>74</v>
       </c>
       <c r="AG283" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="AH283" t="s" s="2">
         <v>75</v>
@@ -34480,13 +34480,13 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D284" s="2"/>
       <c r="E284" t="s" s="2">
@@ -34509,19 +34509,19 @@
         <v>83</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N284" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="O284" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="P284" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="Q284" t="s" s="2">
         <v>74</v>
@@ -34570,7 +34570,7 @@
         <v>74</v>
       </c>
       <c r="AG284" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AH284" t="s" s="2">
         <v>75</v>
@@ -34587,17 +34587,17 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D285" s="2"/>
       <c r="E285" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F285" s="2"/>
       <c r="G285" t="s" s="2">
@@ -34616,17 +34616,17 @@
         <v>83</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="N285" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="O285" s="2"/>
       <c r="P285" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="Q285" t="s" s="2">
         <v>74</v>
@@ -34675,7 +34675,7 @@
         <v>74</v>
       </c>
       <c r="AG285" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AH285" t="s" s="2">
         <v>75</v>
@@ -34692,13 +34692,13 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D286" s="2"/>
       <c r="E286" t="s" s="2">
@@ -34721,17 +34721,17 @@
         <v>83</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="N286" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="O286" s="2"/>
       <c r="P286" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="Q286" t="s" s="2">
         <v>74</v>
@@ -34780,7 +34780,7 @@
         <v>74</v>
       </c>
       <c r="AG286" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="AH286" t="s" s="2">
         <v>75</v>
@@ -34797,13 +34797,13 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" t="s" s="2">
@@ -34829,10 +34829,10 @@
         <v>444</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="N287" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="O287" s="2"/>
       <c r="P287" s="2"/>
@@ -34883,7 +34883,7 @@
         <v>74</v>
       </c>
       <c r="AG287" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="AH287" t="s" s="2">
         <v>75</v>
@@ -34900,17 +34900,17 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F288" s="2"/>
       <c r="G288" t="s" s="2">
@@ -34932,14 +34932,14 @@
         <v>375</v>
       </c>
       <c r="M288" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="N288" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="O288" s="2"/>
       <c r="P288" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="Q288" t="s" s="2">
         <v>74</v>
@@ -34988,7 +34988,7 @@
         <v>74</v>
       </c>
       <c r="AG288" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="AH288" t="s" s="2">
         <v>75</v>
@@ -34997,7 +34997,7 @@
         <v>82</v>
       </c>
       <c r="AJ288" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="AK288" t="s" s="2">
         <v>94</v>
@@ -35005,17 +35005,17 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F289" s="2"/>
       <c r="G289" t="s" s="2">
@@ -35037,14 +35037,14 @@
         <v>375</v>
       </c>
       <c r="M289" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="N289" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="O289" s="2"/>
       <c r="P289" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="Q289" t="s" s="2">
         <v>74</v>
@@ -35093,16 +35093,16 @@
         <v>74</v>
       </c>
       <c r="AG289" t="s" s="2">
+        <v>950</v>
+      </c>
+      <c r="AH289" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI289" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ289" t="s" s="2">
         <v>949</v>
-      </c>
-      <c r="AH289" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI289" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ289" t="s" s="2">
-        <v>948</v>
       </c>
       <c r="AK289" t="s" s="2">
         <v>94</v>
@@ -35110,13 +35110,13 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D290" s="2"/>
       <c r="E290" t="s" s="2">
@@ -35139,17 +35139,17 @@
         <v>83</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="N290" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="O290" s="2"/>
       <c r="P290" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="Q290" t="s" s="2">
         <v>74</v>
@@ -35198,7 +35198,7 @@
         <v>74</v>
       </c>
       <c r="AG290" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AH290" t="s" s="2">
         <v>75</v>
@@ -35215,13 +35215,13 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D291" s="2"/>
       <c r="E291" t="s" s="2">
@@ -35247,14 +35247,14 @@
         <v>357</v>
       </c>
       <c r="M291" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="N291" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="O291" s="2"/>
       <c r="P291" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="Q291" t="s" s="2">
         <v>74</v>
@@ -35282,10 +35282,10 @@
         <v>106</v>
       </c>
       <c r="Z291" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="AA291" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AB291" t="s" s="2">
         <v>74</v>
@@ -35303,7 +35303,7 @@
         <v>74</v>
       </c>
       <c r="AG291" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="AH291" t="s" s="2">
         <v>75</v>
@@ -35320,17 +35320,17 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F292" s="2"/>
       <c r="G292" t="s" s="2">
@@ -35349,19 +35349,19 @@
         <v>83</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="N292" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="O292" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="P292" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="Q292" t="s" s="2">
         <v>74</v>
@@ -35410,7 +35410,7 @@
         <v>74</v>
       </c>
       <c r="AG292" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="AH292" t="s" s="2">
         <v>75</v>
@@ -35427,13 +35427,13 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" t="s" s="2">
@@ -35456,17 +35456,17 @@
         <v>83</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="M293" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="N293" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="O293" s="2"/>
       <c r="P293" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="Q293" t="s" s="2">
         <v>74</v>
@@ -35515,7 +35515,7 @@
         <v>74</v>
       </c>
       <c r="AG293" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="AH293" t="s" s="2">
         <v>75</v>
@@ -35532,13 +35532,13 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D294" s="2"/>
       <c r="E294" t="s" s="2">
@@ -35564,13 +35564,13 @@
         <v>357</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="N294" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="O294" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="P294" s="2"/>
       <c r="Q294" t="s" s="2">
@@ -35599,7 +35599,7 @@
         <v>318</v>
       </c>
       <c r="Z294" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="AA294" t="s" s="2">
         <v>74</v>
@@ -35620,7 +35620,7 @@
         <v>74</v>
       </c>
       <c r="AG294" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="AH294" t="s" s="2">
         <v>75</v>
@@ -35637,13 +35637,13 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D295" s="2"/>
       <c r="E295" t="s" s="2">
@@ -35666,16 +35666,16 @@
         <v>74</v>
       </c>
       <c r="L295" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M295" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="N295" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="O295" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="P295" s="2"/>
       <c r="Q295" t="s" s="2">
@@ -35725,7 +35725,7 @@
         <v>74</v>
       </c>
       <c r="AG295" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="AH295" t="s" s="2">
         <v>75</v>
@@ -35742,13 +35742,13 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" t="s" s="2">
@@ -35771,13 +35771,13 @@
         <v>74</v>
       </c>
       <c r="L296" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M296" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="N296" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="O296" s="2"/>
       <c r="P296" s="2"/>
@@ -35828,7 +35828,7 @@
         <v>74</v>
       </c>
       <c r="AG296" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AH296" t="s" s="2">
         <v>75</v>
@@ -35845,13 +35845,13 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D297" s="2"/>
       <c r="E297" t="s" s="2">
@@ -35874,13 +35874,13 @@
         <v>74</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M297" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="N297" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="O297" s="2"/>
       <c r="P297" s="2"/>
@@ -35931,7 +35931,7 @@
         <v>74</v>
       </c>
       <c r="AG297" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="AH297" t="s" s="2">
         <v>75</v>
@@ -35948,17 +35948,17 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D298" s="2"/>
       <c r="E298" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F298" s="2"/>
       <c r="G298" t="s" s="2">
@@ -35977,16 +35977,16 @@
         <v>74</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M298" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="N298" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="O298" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P298" s="2"/>
       <c r="Q298" t="s" s="2">
@@ -36036,7 +36036,7 @@
         <v>74</v>
       </c>
       <c r="AG298" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="AH298" t="s" s="2">
         <v>75</v>
@@ -36053,13 +36053,13 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D299" s="2"/>
       <c r="E299" t="s" s="2">
@@ -36085,14 +36085,14 @@
         <v>135</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="N299" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="O299" s="2"/>
       <c r="P299" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="Q299" t="s" s="2">
         <v>74</v>
@@ -36141,7 +36141,7 @@
         <v>74</v>
       </c>
       <c r="AG299" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="AH299" t="s" s="2">
         <v>75</v>
@@ -36158,13 +36158,13 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" t="s" s="2">
@@ -36261,13 +36261,13 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D301" s="2"/>
       <c r="E301" t="s" s="2">
@@ -36366,13 +36366,13 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D302" s="2"/>
       <c r="E302" t="s" s="2">
@@ -36473,13 +36473,13 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D303" s="2"/>
       <c r="E303" t="s" s="2">
@@ -36502,17 +36502,17 @@
         <v>74</v>
       </c>
       <c r="L303" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M303" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="N303" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="O303" s="2"/>
       <c r="P303" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="Q303" t="s" s="2">
         <v>74</v>
@@ -36561,7 +36561,7 @@
         <v>74</v>
       </c>
       <c r="AG303" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="AH303" t="s" s="2">
         <v>75</v>
@@ -36578,13 +36578,13 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" t="s" s="2">
@@ -36610,16 +36610,16 @@
         <v>444</v>
       </c>
       <c r="M304" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="N304" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="O304" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="P304" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="Q304" t="s" s="2">
         <v>74</v>
@@ -36668,7 +36668,7 @@
         <v>74</v>
       </c>
       <c r="AG304" t="s" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="AH304" t="s" s="2">
         <v>75</v>
@@ -36685,13 +36685,13 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" t="s" s="2">
@@ -36714,13 +36714,13 @@
         <v>74</v>
       </c>
       <c r="L305" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="M305" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N305" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="O305" s="2"/>
       <c r="P305" s="2"/>
@@ -36771,7 +36771,7 @@
         <v>74</v>
       </c>
       <c r="AG305" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="AH305" t="s" s="2">
         <v>75</v>
@@ -36788,21 +36788,21 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F306" s="2"/>
       <c r="G306" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H306" t="s" s="2">
         <v>76</v>
@@ -36820,14 +36820,14 @@
         <v>135</v>
       </c>
       <c r="M306" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="N306" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O306" s="2"/>
       <c r="P306" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q306" t="s" s="2">
         <v>74</v>
@@ -36864,7 +36864,7 @@
         <v>74</v>
       </c>
       <c r="AC306" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="AD306" s="2"/>
       <c r="AE306" t="s" s="2">
@@ -36874,7 +36874,7 @@
         <v>283</v>
       </c>
       <c r="AG306" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH306" t="s" s="2">
         <v>75</v>
@@ -36891,13 +36891,13 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" t="s" s="2">
@@ -36994,13 +36994,13 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" t="s" s="2">
@@ -37099,13 +37099,13 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" t="s" s="2">
@@ -37206,17 +37206,17 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F310" s="2"/>
       <c r="G310" t="s" s="2">
@@ -37238,16 +37238,16 @@
         <v>357</v>
       </c>
       <c r="M310" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N310" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O310" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P310" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q310" t="s" s="2">
         <v>74</v>
@@ -37275,7 +37275,7 @@
         <v>318</v>
       </c>
       <c r="Z310" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA310" t="s" s="2">
         <v>74</v>
@@ -37296,7 +37296,7 @@
         <v>74</v>
       </c>
       <c r="AG310" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH310" t="s" s="2">
         <v>82</v>
@@ -37313,13 +37313,13 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" t="s" s="2">
@@ -37342,13 +37342,13 @@
         <v>74</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N311" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O311" s="2"/>
       <c r="P311" s="2"/>
@@ -37399,7 +37399,7 @@
         <v>74</v>
       </c>
       <c r="AG311" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH311" t="s" s="2">
         <v>82</v>
@@ -37416,19 +37416,19 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D312" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E312" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F312" s="2"/>
       <c r="G312" t="s" s="2">
@@ -37450,14 +37450,14 @@
         <v>135</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="N312" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O312" s="2"/>
       <c r="P312" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q312" t="s" s="2">
         <v>74</v>
@@ -37506,7 +37506,7 @@
         <v>74</v>
       </c>
       <c r="AG312" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH312" t="s" s="2">
         <v>75</v>
@@ -37523,13 +37523,13 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" t="s" s="2">
@@ -37626,13 +37626,13 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" t="s" s="2">
@@ -37731,13 +37731,13 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" t="s" s="2">
@@ -37838,17 +37838,17 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F316" s="2"/>
       <c r="G316" t="s" s="2">
@@ -37870,16 +37870,16 @@
         <v>357</v>
       </c>
       <c r="M316" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N316" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O316" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P316" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q316" t="s" s="2">
         <v>74</v>
@@ -37889,7 +37889,7 @@
         <v>74</v>
       </c>
       <c r="T316" t="s" s="2">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="U316" t="s" s="2">
         <v>74</v>
@@ -37907,7 +37907,7 @@
         <v>318</v>
       </c>
       <c r="Z316" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA316" t="s" s="2">
         <v>74</v>
@@ -37928,7 +37928,7 @@
         <v>74</v>
       </c>
       <c r="AG316" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH316" t="s" s="2">
         <v>82</v>
@@ -37945,13 +37945,13 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" t="s" s="2">
@@ -37977,10 +37977,10 @@
         <v>111</v>
       </c>
       <c r="M317" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N317" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O317" s="2"/>
       <c r="P317" s="2"/>
@@ -38031,7 +38031,7 @@
         <v>74</v>
       </c>
       <c r="AG317" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH317" t="s" s="2">
         <v>82</v>
@@ -38048,19 +38048,19 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D318" t="s" s="2">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E318" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F318" s="2"/>
       <c r="G318" t="s" s="2">
@@ -38082,14 +38082,14 @@
         <v>135</v>
       </c>
       <c r="M318" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="N318" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O318" s="2"/>
       <c r="P318" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q318" t="s" s="2">
         <v>74</v>
@@ -38138,7 +38138,7 @@
         <v>74</v>
       </c>
       <c r="AG318" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH318" t="s" s="2">
         <v>75</v>
@@ -38155,13 +38155,13 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" t="s" s="2">
@@ -38258,13 +38258,13 @@
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" t="s" s="2">
@@ -38363,13 +38363,13 @@
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" t="s" s="2">
@@ -38470,17 +38470,17 @@
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F322" s="2"/>
       <c r="G322" t="s" s="2">
@@ -38502,16 +38502,16 @@
         <v>357</v>
       </c>
       <c r="M322" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N322" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O322" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P322" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q322" t="s" s="2">
         <v>74</v>
@@ -38521,7 +38521,7 @@
         <v>74</v>
       </c>
       <c r="T322" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="U322" t="s" s="2">
         <v>74</v>
@@ -38539,7 +38539,7 @@
         <v>318</v>
       </c>
       <c r="Z322" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA322" t="s" s="2">
         <v>74</v>
@@ -38560,7 +38560,7 @@
         <v>74</v>
       </c>
       <c r="AG322" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH322" t="s" s="2">
         <v>82</v>
@@ -38577,13 +38577,13 @@
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" t="s" s="2">
@@ -38609,10 +38609,10 @@
         <v>140</v>
       </c>
       <c r="M323" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N323" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O323" s="2"/>
       <c r="P323" s="2"/>
@@ -38663,7 +38663,7 @@
         <v>74</v>
       </c>
       <c r="AG323" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH323" t="s" s="2">
         <v>82</v>
@@ -38680,19 +38680,19 @@
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D324" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="E324" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F324" s="2"/>
       <c r="G324" t="s" s="2">
@@ -38714,14 +38714,14 @@
         <v>135</v>
       </c>
       <c r="M324" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="N324" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O324" s="2"/>
       <c r="P324" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q324" t="s" s="2">
         <v>74</v>
@@ -38770,7 +38770,7 @@
         <v>74</v>
       </c>
       <c r="AG324" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH324" t="s" s="2">
         <v>75</v>
@@ -38787,13 +38787,13 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" t="s" s="2">
@@ -38890,13 +38890,13 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" t="s" s="2">
@@ -38995,13 +38995,13 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" t="s" s="2">
@@ -39102,17 +39102,17 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F328" s="2"/>
       <c r="G328" t="s" s="2">
@@ -39134,16 +39134,16 @@
         <v>357</v>
       </c>
       <c r="M328" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N328" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O328" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P328" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q328" t="s" s="2">
         <v>74</v>
@@ -39153,7 +39153,7 @@
         <v>74</v>
       </c>
       <c r="T328" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="U328" t="s" s="2">
         <v>74</v>
@@ -39171,7 +39171,7 @@
         <v>318</v>
       </c>
       <c r="Z328" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA328" t="s" s="2">
         <v>74</v>
@@ -39192,7 +39192,7 @@
         <v>74</v>
       </c>
       <c r="AG328" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH328" t="s" s="2">
         <v>82</v>
@@ -39209,13 +39209,13 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" t="s" s="2">
@@ -39241,10 +39241,10 @@
         <v>357</v>
       </c>
       <c r="M329" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N329" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O329" s="2"/>
       <c r="P329" s="2"/>
@@ -39275,7 +39275,7 @@
       </c>
       <c r="Z329" s="2"/>
       <c r="AA329" t="s" s="2">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="AB329" t="s" s="2">
         <v>74</v>
@@ -39293,7 +39293,7 @@
         <v>74</v>
       </c>
       <c r="AG329" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH329" t="s" s="2">
         <v>82</v>
@@ -39310,19 +39310,19 @@
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D330" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="E330" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F330" s="2"/>
       <c r="G330" t="s" s="2">
@@ -39344,14 +39344,14 @@
         <v>135</v>
       </c>
       <c r="M330" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="N330" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O330" s="2"/>
       <c r="P330" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q330" t="s" s="2">
         <v>74</v>
@@ -39400,7 +39400,7 @@
         <v>74</v>
       </c>
       <c r="AG330" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH330" t="s" s="2">
         <v>75</v>
@@ -39417,13 +39417,13 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" t="s" s="2">
@@ -39520,13 +39520,13 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" t="s" s="2">
@@ -39625,13 +39625,13 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" t="s" s="2">
@@ -39732,17 +39732,17 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F334" s="2"/>
       <c r="G334" t="s" s="2">
@@ -39764,16 +39764,16 @@
         <v>357</v>
       </c>
       <c r="M334" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N334" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O334" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P334" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q334" t="s" s="2">
         <v>74</v>
@@ -39783,7 +39783,7 @@
         <v>74</v>
       </c>
       <c r="T334" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="U334" t="s" s="2">
         <v>74</v>
@@ -39801,7 +39801,7 @@
         <v>318</v>
       </c>
       <c r="Z334" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA334" t="s" s="2">
         <v>74</v>
@@ -39822,7 +39822,7 @@
         <v>74</v>
       </c>
       <c r="AG334" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH334" t="s" s="2">
         <v>82</v>
@@ -39839,13 +39839,13 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" t="s" s="2">
@@ -39871,10 +39871,10 @@
         <v>357</v>
       </c>
       <c r="M335" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="N335" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O335" s="2"/>
       <c r="P335" s="2"/>
@@ -39905,7 +39905,7 @@
       </c>
       <c r="Z335" s="2"/>
       <c r="AA335" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AB335" t="s" s="2">
         <v>74</v>
@@ -39923,7 +39923,7 @@
         <v>74</v>
       </c>
       <c r="AG335" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH335" t="s" s="2">
         <v>82</v>
@@ -39940,19 +39940,19 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D336" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E336" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F336" s="2"/>
       <c r="G336" t="s" s="2">
@@ -39974,14 +39974,14 @@
         <v>135</v>
       </c>
       <c r="M336" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="N336" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O336" s="2"/>
       <c r="P336" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q336" t="s" s="2">
         <v>74</v>
@@ -40030,7 +40030,7 @@
         <v>74</v>
       </c>
       <c r="AG336" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH336" t="s" s="2">
         <v>75</v>
@@ -40047,13 +40047,13 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" t="s" s="2">
@@ -40150,13 +40150,13 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" t="s" s="2">
@@ -40255,13 +40255,13 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" t="s" s="2">
@@ -40362,17 +40362,17 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F340" s="2"/>
       <c r="G340" t="s" s="2">
@@ -40394,16 +40394,16 @@
         <v>357</v>
       </c>
       <c r="M340" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N340" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O340" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P340" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q340" t="s" s="2">
         <v>74</v>
@@ -40413,7 +40413,7 @@
         <v>74</v>
       </c>
       <c r="T340" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="U340" t="s" s="2">
         <v>74</v>
@@ -40431,7 +40431,7 @@
         <v>318</v>
       </c>
       <c r="Z340" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA340" t="s" s="2">
         <v>74</v>
@@ -40452,7 +40452,7 @@
         <v>74</v>
       </c>
       <c r="AG340" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH340" t="s" s="2">
         <v>82</v>
@@ -40469,13 +40469,13 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" t="s" s="2">
@@ -40498,13 +40498,13 @@
         <v>74</v>
       </c>
       <c r="L341" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="M341" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N341" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O341" s="2"/>
       <c r="P341" s="2"/>
@@ -40555,7 +40555,7 @@
         <v>74</v>
       </c>
       <c r="AG341" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH341" t="s" s="2">
         <v>82</v>
@@ -40572,19 +40572,19 @@
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D342" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E342" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F342" s="2"/>
       <c r="G342" t="s" s="2">
@@ -40606,14 +40606,14 @@
         <v>135</v>
       </c>
       <c r="M342" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="N342" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O342" s="2"/>
       <c r="P342" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q342" t="s" s="2">
         <v>74</v>
@@ -40662,7 +40662,7 @@
         <v>74</v>
       </c>
       <c r="AG342" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH342" t="s" s="2">
         <v>75</v>
@@ -40679,13 +40679,13 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D343" s="2"/>
       <c r="E343" t="s" s="2">
@@ -40782,13 +40782,13 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D344" s="2"/>
       <c r="E344" t="s" s="2">
@@ -40887,13 +40887,13 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" t="s" s="2">
@@ -40994,17 +40994,17 @@
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F346" s="2"/>
       <c r="G346" t="s" s="2">
@@ -41026,16 +41026,16 @@
         <v>357</v>
       </c>
       <c r="M346" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N346" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O346" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P346" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q346" t="s" s="2">
         <v>74</v>
@@ -41045,7 +41045,7 @@
         <v>74</v>
       </c>
       <c r="T346" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="U346" t="s" s="2">
         <v>74</v>
@@ -41063,7 +41063,7 @@
         <v>318</v>
       </c>
       <c r="Z346" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA346" t="s" s="2">
         <v>74</v>
@@ -41084,7 +41084,7 @@
         <v>74</v>
       </c>
       <c r="AG346" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH346" t="s" s="2">
         <v>82</v>
@@ -41101,13 +41101,13 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" t="s" s="2">
@@ -41133,10 +41133,10 @@
         <v>111</v>
       </c>
       <c r="M347" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N347" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O347" s="2"/>
       <c r="P347" s="2"/>
@@ -41187,7 +41187,7 @@
         <v>74</v>
       </c>
       <c r="AG347" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH347" t="s" s="2">
         <v>82</v>
@@ -41204,19 +41204,19 @@
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D348" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="E348" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F348" s="2"/>
       <c r="G348" t="s" s="2">
@@ -41238,14 +41238,14 @@
         <v>135</v>
       </c>
       <c r="M348" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="N348" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O348" s="2"/>
       <c r="P348" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q348" t="s" s="2">
         <v>74</v>
@@ -41294,7 +41294,7 @@
         <v>74</v>
       </c>
       <c r="AG348" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH348" t="s" s="2">
         <v>75</v>
@@ -41311,13 +41311,13 @@
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" t="s" s="2">
@@ -41414,13 +41414,13 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D350" s="2"/>
       <c r="E350" t="s" s="2">
@@ -41519,13 +41519,13 @@
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" t="s" s="2">
@@ -41626,17 +41626,17 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F352" s="2"/>
       <c r="G352" t="s" s="2">
@@ -41658,16 +41658,16 @@
         <v>357</v>
       </c>
       <c r="M352" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N352" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O352" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P352" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q352" t="s" s="2">
         <v>74</v>
@@ -41677,7 +41677,7 @@
         <v>74</v>
       </c>
       <c r="T352" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="U352" t="s" s="2">
         <v>74</v>
@@ -41695,7 +41695,7 @@
         <v>318</v>
       </c>
       <c r="Z352" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA352" t="s" s="2">
         <v>74</v>
@@ -41716,7 +41716,7 @@
         <v>74</v>
       </c>
       <c r="AG352" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH352" t="s" s="2">
         <v>82</v>
@@ -41733,13 +41733,13 @@
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" t="s" s="2">
@@ -41765,10 +41765,10 @@
         <v>140</v>
       </c>
       <c r="M353" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N353" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O353" s="2"/>
       <c r="P353" s="2"/>
@@ -41819,7 +41819,7 @@
         <v>74</v>
       </c>
       <c r="AG353" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH353" t="s" s="2">
         <v>82</v>
@@ -41836,19 +41836,19 @@
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D354" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E354" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F354" s="2"/>
       <c r="G354" t="s" s="2">
@@ -41870,14 +41870,14 @@
         <v>135</v>
       </c>
       <c r="M354" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="N354" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O354" s="2"/>
       <c r="P354" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q354" t="s" s="2">
         <v>74</v>
@@ -41926,7 +41926,7 @@
         <v>74</v>
       </c>
       <c r="AG354" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH354" t="s" s="2">
         <v>75</v>
@@ -41943,13 +41943,13 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" t="s" s="2">
@@ -42046,13 +42046,13 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" t="s" s="2">
@@ -42151,13 +42151,13 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" t="s" s="2">
@@ -42258,17 +42258,17 @@
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F358" s="2"/>
       <c r="G358" t="s" s="2">
@@ -42290,16 +42290,16 @@
         <v>357</v>
       </c>
       <c r="M358" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N358" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O358" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P358" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q358" t="s" s="2">
         <v>74</v>
@@ -42309,7 +42309,7 @@
         <v>74</v>
       </c>
       <c r="T358" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="U358" t="s" s="2">
         <v>74</v>
@@ -42327,7 +42327,7 @@
         <v>318</v>
       </c>
       <c r="Z358" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA358" t="s" s="2">
         <v>74</v>
@@ -42348,7 +42348,7 @@
         <v>74</v>
       </c>
       <c r="AG358" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH358" t="s" s="2">
         <v>82</v>
@@ -42365,13 +42365,13 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" t="s" s="2">
@@ -42397,10 +42397,10 @@
         <v>357</v>
       </c>
       <c r="M359" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N359" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O359" s="2"/>
       <c r="P359" s="2"/>
@@ -42431,7 +42431,7 @@
       </c>
       <c r="Z359" s="2"/>
       <c r="AA359" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AB359" t="s" s="2">
         <v>74</v>
@@ -42449,7 +42449,7 @@
         <v>74</v>
       </c>
       <c r="AG359" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH359" t="s" s="2">
         <v>82</v>
@@ -42466,19 +42466,19 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D360" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E360" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F360" s="2"/>
       <c r="G360" t="s" s="2">
@@ -42500,14 +42500,14 @@
         <v>135</v>
       </c>
       <c r="M360" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="N360" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O360" s="2"/>
       <c r="P360" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q360" t="s" s="2">
         <v>74</v>
@@ -42556,7 +42556,7 @@
         <v>74</v>
       </c>
       <c r="AG360" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH360" t="s" s="2">
         <v>75</v>
@@ -42573,13 +42573,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" t="s" s="2">
@@ -42676,13 +42676,13 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D362" s="2"/>
       <c r="E362" t="s" s="2">
@@ -42781,13 +42781,13 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" t="s" s="2">
@@ -42888,17 +42888,17 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D364" s="2"/>
       <c r="E364" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F364" s="2"/>
       <c r="G364" t="s" s="2">
@@ -42920,16 +42920,16 @@
         <v>357</v>
       </c>
       <c r="M364" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N364" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O364" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P364" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q364" t="s" s="2">
         <v>74</v>
@@ -42939,7 +42939,7 @@
         <v>74</v>
       </c>
       <c r="T364" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="U364" t="s" s="2">
         <v>74</v>
@@ -42957,7 +42957,7 @@
         <v>318</v>
       </c>
       <c r="Z364" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA364" t="s" s="2">
         <v>74</v>
@@ -42978,7 +42978,7 @@
         <v>74</v>
       </c>
       <c r="AG364" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH364" t="s" s="2">
         <v>82</v>
@@ -42995,13 +42995,13 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D365" s="2"/>
       <c r="E365" t="s" s="2">
@@ -43027,10 +43027,10 @@
         <v>357</v>
       </c>
       <c r="M365" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N365" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O365" s="2"/>
       <c r="P365" s="2"/>
@@ -43061,7 +43061,7 @@
       </c>
       <c r="Z365" s="2"/>
       <c r="AA365" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="AB365" t="s" s="2">
         <v>74</v>
@@ -43079,7 +43079,7 @@
         <v>74</v>
       </c>
       <c r="AG365" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH365" t="s" s="2">
         <v>82</v>
@@ -43096,19 +43096,19 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D366" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E366" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F366" s="2"/>
       <c r="G366" t="s" s="2">
@@ -43130,14 +43130,14 @@
         <v>135</v>
       </c>
       <c r="M366" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="N366" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O366" s="2"/>
       <c r="P366" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q366" t="s" s="2">
         <v>74</v>
@@ -43186,7 +43186,7 @@
         <v>74</v>
       </c>
       <c r="AG366" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH366" t="s" s="2">
         <v>75</v>
@@ -43203,13 +43203,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" t="s" s="2">
@@ -43306,13 +43306,13 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D368" s="2"/>
       <c r="E368" t="s" s="2">
@@ -43411,13 +43411,13 @@
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D369" s="2"/>
       <c r="E369" t="s" s="2">
@@ -43518,17 +43518,17 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F370" s="2"/>
       <c r="G370" t="s" s="2">
@@ -43550,16 +43550,16 @@
         <v>357</v>
       </c>
       <c r="M370" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N370" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O370" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P370" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q370" t="s" s="2">
         <v>74</v>
@@ -43569,7 +43569,7 @@
         <v>74</v>
       </c>
       <c r="T370" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="U370" t="s" s="2">
         <v>74</v>
@@ -43587,7 +43587,7 @@
         <v>318</v>
       </c>
       <c r="Z370" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA370" t="s" s="2">
         <v>74</v>
@@ -43608,7 +43608,7 @@
         <v>74</v>
       </c>
       <c r="AG370" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH370" t="s" s="2">
         <v>82</v>
@@ -43625,13 +43625,13 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" t="s" s="2">
@@ -43657,10 +43657,10 @@
         <v>422</v>
       </c>
       <c r="M371" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N371" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O371" s="2"/>
       <c r="P371" s="2"/>
@@ -43711,7 +43711,7 @@
         <v>74</v>
       </c>
       <c r="AG371" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH371" t="s" s="2">
         <v>82</v>
@@ -43728,19 +43728,19 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D372" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="E372" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F372" s="2"/>
       <c r="G372" t="s" s="2">
@@ -43762,14 +43762,14 @@
         <v>135</v>
       </c>
       <c r="M372" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="N372" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O372" s="2"/>
       <c r="P372" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q372" t="s" s="2">
         <v>74</v>
@@ -43818,7 +43818,7 @@
         <v>74</v>
       </c>
       <c r="AG372" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH372" t="s" s="2">
         <v>75</v>
@@ -43830,18 +43830,18 @@
         <v>74</v>
       </c>
       <c r="AK372" t="s" s="2">
-        <v>1140</v>
+        <v>94</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B373" t="s" s="2">
         <v>1141</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D373" s="2"/>
       <c r="E373" t="s" s="2">
@@ -43938,13 +43938,13 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B374" t="s" s="2">
         <v>1142</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D374" s="2"/>
       <c r="E374" t="s" s="2">
@@ -44043,13 +44043,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B375" t="s" s="2">
         <v>1143</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" t="s" s="2">
@@ -44150,17 +44150,17 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B376" t="s" s="2">
         <v>1144</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F376" s="2"/>
       <c r="G376" t="s" s="2">
@@ -44182,16 +44182,16 @@
         <v>357</v>
       </c>
       <c r="M376" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N376" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O376" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P376" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q376" t="s" s="2">
         <v>74</v>
@@ -44219,7 +44219,7 @@
         <v>318</v>
       </c>
       <c r="Z376" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA376" t="s" s="2">
         <v>74</v>
@@ -44240,7 +44240,7 @@
         <v>74</v>
       </c>
       <c r="AG376" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH376" t="s" s="2">
         <v>82</v>
@@ -44257,13 +44257,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B377" t="s" s="2">
         <v>1146</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" t="s" s="2">
@@ -44289,10 +44289,10 @@
         <v>357</v>
       </c>
       <c r="M377" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N377" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O377" s="2"/>
       <c r="P377" s="2"/>
@@ -44341,7 +44341,7 @@
         <v>74</v>
       </c>
       <c r="AG377" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH377" t="s" s="2">
         <v>82</v>
@@ -44358,7 +44358,7 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B378" t="s" s="2">
         <v>1148</v>
@@ -44461,7 +44461,7 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B379" t="s" s="2">
         <v>1150</v>
@@ -44566,7 +44566,7 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B380" t="s" s="2">
         <v>1152</v>
@@ -44673,7 +44673,7 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B381" t="s" s="2">
         <v>1154</v>
@@ -44780,19 +44780,19 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B382" t="s" s="2">
         <v>1156</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D382" t="s" s="2">
         <v>1157</v>
       </c>
       <c r="E382" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F382" s="2"/>
       <c r="G382" t="s" s="2">
@@ -44817,11 +44817,11 @@
         <v>1158</v>
       </c>
       <c r="N382" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O382" s="2"/>
       <c r="P382" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q382" t="s" s="2">
         <v>74</v>
@@ -44870,7 +44870,7 @@
         <v>74</v>
       </c>
       <c r="AG382" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH382" t="s" s="2">
         <v>75</v>
@@ -44887,13 +44887,13 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B383" t="s" s="2">
         <v>1159</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" t="s" s="2">
@@ -44990,13 +44990,13 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B384" t="s" s="2">
         <v>1160</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" t="s" s="2">
@@ -45095,13 +45095,13 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B385" t="s" s="2">
         <v>1161</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" t="s" s="2">
@@ -45202,17 +45202,17 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B386" t="s" s="2">
         <v>1162</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D386" s="2"/>
       <c r="E386" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F386" s="2"/>
       <c r="G386" t="s" s="2">
@@ -45234,16 +45234,16 @@
         <v>357</v>
       </c>
       <c r="M386" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N386" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O386" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P386" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q386" t="s" s="2">
         <v>74</v>
@@ -45271,7 +45271,7 @@
         <v>318</v>
       </c>
       <c r="Z386" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA386" t="s" s="2">
         <v>74</v>
@@ -45292,7 +45292,7 @@
         <v>74</v>
       </c>
       <c r="AG386" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH386" t="s" s="2">
         <v>82</v>
@@ -45309,13 +45309,13 @@
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B387" t="s" s="2">
         <v>1164</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" t="s" s="2">
@@ -45341,10 +45341,10 @@
         <v>357</v>
       </c>
       <c r="M387" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N387" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O387" s="2"/>
       <c r="P387" s="2"/>
@@ -45393,7 +45393,7 @@
         <v>74</v>
       </c>
       <c r="AG387" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH387" t="s" s="2">
         <v>82</v>
@@ -45410,19 +45410,19 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B388" t="s" s="2">
         <v>1166</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D388" t="s" s="2">
         <v>1167</v>
       </c>
       <c r="E388" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F388" s="2"/>
       <c r="G388" t="s" s="2">
@@ -45447,11 +45447,11 @@
         <v>1168</v>
       </c>
       <c r="N388" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O388" s="2"/>
       <c r="P388" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q388" t="s" s="2">
         <v>74</v>
@@ -45500,7 +45500,7 @@
         <v>74</v>
       </c>
       <c r="AG388" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH388" t="s" s="2">
         <v>75</v>
@@ -45517,13 +45517,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B389" t="s" s="2">
         <v>1169</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" t="s" s="2">
@@ -45620,13 +45620,13 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B390" t="s" s="2">
         <v>1170</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D390" s="2"/>
       <c r="E390" t="s" s="2">
@@ -45725,13 +45725,13 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B391" t="s" s="2">
         <v>1171</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D391" s="2"/>
       <c r="E391" t="s" s="2">
@@ -45832,17 +45832,17 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B392" t="s" s="2">
         <v>1172</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D392" s="2"/>
       <c r="E392" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F392" s="2"/>
       <c r="G392" t="s" s="2">
@@ -45864,16 +45864,16 @@
         <v>357</v>
       </c>
       <c r="M392" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N392" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O392" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P392" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q392" t="s" s="2">
         <v>74</v>
@@ -45901,7 +45901,7 @@
         <v>318</v>
       </c>
       <c r="Z392" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA392" t="s" s="2">
         <v>74</v>
@@ -45922,7 +45922,7 @@
         <v>74</v>
       </c>
       <c r="AG392" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH392" t="s" s="2">
         <v>82</v>
@@ -45939,13 +45939,13 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B393" t="s" s="2">
         <v>1174</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D393" s="2"/>
       <c r="E393" t="s" s="2">
@@ -45968,13 +45968,13 @@
         <v>74</v>
       </c>
       <c r="L393" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="M393" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N393" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O393" s="2"/>
       <c r="P393" s="2"/>
@@ -46025,7 +46025,7 @@
         <v>74</v>
       </c>
       <c r="AG393" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH393" t="s" s="2">
         <v>82</v>
@@ -46042,19 +46042,19 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B394" t="s" s="2">
         <v>1175</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D394" t="s" s="2">
         <v>1176</v>
       </c>
       <c r="E394" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F394" s="2"/>
       <c r="G394" t="s" s="2">
@@ -46079,11 +46079,11 @@
         <v>1177</v>
       </c>
       <c r="N394" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O394" s="2"/>
       <c r="P394" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q394" t="s" s="2">
         <v>74</v>
@@ -46132,7 +46132,7 @@
         <v>74</v>
       </c>
       <c r="AG394" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH394" t="s" s="2">
         <v>75</v>
@@ -46149,13 +46149,13 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B395" t="s" s="2">
         <v>1178</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D395" s="2"/>
       <c r="E395" t="s" s="2">
@@ -46252,13 +46252,13 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B396" t="s" s="2">
         <v>1179</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D396" s="2"/>
       <c r="E396" t="s" s="2">
@@ -46357,13 +46357,13 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B397" t="s" s="2">
         <v>1180</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D397" s="2"/>
       <c r="E397" t="s" s="2">
@@ -46464,17 +46464,17 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B398" t="s" s="2">
         <v>1181</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D398" s="2"/>
       <c r="E398" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F398" s="2"/>
       <c r="G398" t="s" s="2">
@@ -46496,16 +46496,16 @@
         <v>357</v>
       </c>
       <c r="M398" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N398" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O398" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P398" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q398" t="s" s="2">
         <v>74</v>
@@ -46533,7 +46533,7 @@
         <v>318</v>
       </c>
       <c r="Z398" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA398" t="s" s="2">
         <v>74</v>
@@ -46554,7 +46554,7 @@
         <v>74</v>
       </c>
       <c r="AG398" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH398" t="s" s="2">
         <v>82</v>
@@ -46571,13 +46571,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B399" t="s" s="2">
         <v>1183</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D399" s="2"/>
       <c r="E399" t="s" s="2">
@@ -46606,7 +46606,7 @@
         <v>1184</v>
       </c>
       <c r="N399" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O399" s="2"/>
       <c r="P399" s="2"/>
@@ -46655,7 +46655,7 @@
         <v>74</v>
       </c>
       <c r="AG399" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH399" t="s" s="2">
         <v>82</v>
@@ -46672,19 +46672,19 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B400" t="s" s="2">
         <v>1186</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D400" t="s" s="2">
         <v>610</v>
       </c>
       <c r="E400" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F400" s="2"/>
       <c r="G400" t="s" s="2">
@@ -46709,11 +46709,11 @@
         <v>1187</v>
       </c>
       <c r="N400" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O400" s="2"/>
       <c r="P400" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q400" t="s" s="2">
         <v>74</v>
@@ -46762,7 +46762,7 @@
         <v>74</v>
       </c>
       <c r="AG400" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH400" t="s" s="2">
         <v>75</v>
@@ -46779,13 +46779,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B401" t="s" s="2">
         <v>1188</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D401" s="2"/>
       <c r="E401" t="s" s="2">
@@ -46882,13 +46882,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B402" t="s" s="2">
         <v>1189</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D402" s="2"/>
       <c r="E402" t="s" s="2">
@@ -46987,13 +46987,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B403" t="s" s="2">
         <v>1190</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D403" s="2"/>
       <c r="E403" t="s" s="2">
@@ -47094,17 +47094,17 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B404" t="s" s="2">
         <v>1191</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D404" s="2"/>
       <c r="E404" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F404" s="2"/>
       <c r="G404" t="s" s="2">
@@ -47126,16 +47126,16 @@
         <v>357</v>
       </c>
       <c r="M404" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N404" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O404" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P404" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q404" t="s" s="2">
         <v>74</v>
@@ -47163,7 +47163,7 @@
         <v>318</v>
       </c>
       <c r="Z404" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA404" t="s" s="2">
         <v>74</v>
@@ -47184,7 +47184,7 @@
         <v>74</v>
       </c>
       <c r="AG404" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH404" t="s" s="2">
         <v>82</v>
@@ -47201,13 +47201,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B405" t="s" s="2">
         <v>1193</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D405" s="2"/>
       <c r="E405" t="s" s="2">
@@ -47233,10 +47233,10 @@
         <v>111</v>
       </c>
       <c r="M405" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N405" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O405" s="2"/>
       <c r="P405" s="2"/>
@@ -47287,7 +47287,7 @@
         <v>74</v>
       </c>
       <c r="AG405" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH405" t="s" s="2">
         <v>82</v>
@@ -47304,19 +47304,19 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B406" t="s" s="2">
         <v>1194</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D406" t="s" s="2">
         <v>631</v>
       </c>
       <c r="E406" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F406" s="2"/>
       <c r="G406" t="s" s="2">
@@ -47341,11 +47341,11 @@
         <v>1195</v>
       </c>
       <c r="N406" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O406" s="2"/>
       <c r="P406" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q406" t="s" s="2">
         <v>74</v>
@@ -47394,7 +47394,7 @@
         <v>74</v>
       </c>
       <c r="AG406" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH406" t="s" s="2">
         <v>75</v>
@@ -47411,13 +47411,13 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B407" t="s" s="2">
         <v>1196</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D407" s="2"/>
       <c r="E407" t="s" s="2">
@@ -47514,13 +47514,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B408" t="s" s="2">
         <v>1197</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D408" s="2"/>
       <c r="E408" t="s" s="2">
@@ -47619,13 +47619,13 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B409" t="s" s="2">
         <v>1198</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D409" s="2"/>
       <c r="E409" t="s" s="2">
@@ -47726,17 +47726,17 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B410" t="s" s="2">
         <v>1199</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D410" s="2"/>
       <c r="E410" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F410" s="2"/>
       <c r="G410" t="s" s="2">
@@ -47758,16 +47758,16 @@
         <v>357</v>
       </c>
       <c r="M410" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N410" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O410" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P410" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="Q410" t="s" s="2">
         <v>74</v>
@@ -47795,7 +47795,7 @@
         <v>318</v>
       </c>
       <c r="Z410" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA410" t="s" s="2">
         <v>74</v>
@@ -47816,7 +47816,7 @@
         <v>74</v>
       </c>
       <c r="AG410" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH410" t="s" s="2">
         <v>82</v>
@@ -47833,13 +47833,13 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B411" t="s" s="2">
         <v>1201</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D411" s="2"/>
       <c r="E411" t="s" s="2">
@@ -47865,10 +47865,10 @@
         <v>111</v>
       </c>
       <c r="M411" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N411" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O411" s="2"/>
       <c r="P411" s="2"/>
@@ -47919,7 +47919,7 @@
         <v>74</v>
       </c>
       <c r="AG411" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH411" t="s" s="2">
         <v>82</v>
@@ -47936,7 +47936,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B412" t="s" s="2">
         <v>1202</v>
@@ -48041,7 +48041,7 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B413" t="s" s="2">
         <v>1206</v>
@@ -48144,7 +48144,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B414" t="s" s="2">
         <v>1207</v>
@@ -48249,7 +48249,7 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B415" t="s" s="2">
         <v>1208</v>
@@ -48356,7 +48356,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B416" t="s" s="2">
         <v>1209</v>
@@ -48366,7 +48366,7 @@
       </c>
       <c r="D416" s="2"/>
       <c r="E416" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F416" s="2"/>
       <c r="G416" t="s" s="2">
@@ -48461,7 +48461,7 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B417" t="s" s="2">
         <v>1214</v>
@@ -48490,7 +48490,7 @@
         <v>74</v>
       </c>
       <c r="L417" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="M417" t="s" s="2">
         <v>1215</v>
